--- a/AAII_Financials/Quarterly/ZIJMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIJMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>ZIJMY</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,8 +1170,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1290,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1340,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1397,8 +1440,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +1590,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1890,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1961,60 +2040,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,431 +2137,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13443300</v>
+      </c>
+      <c r="E41" s="3">
         <v>14410200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9375600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9564600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4987200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5542800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4341800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3732900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3466400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2928900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2601700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2362400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2851500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2755900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2935100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2886300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1858300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2186000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1377500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1647700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>839300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1281600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1050300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>961000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>755100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>859100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>751300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1018600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>897000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>949700</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2839000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2176300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2590200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1954400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2608800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2076200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2250300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1972700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2470900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2067800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2552400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2008500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2243600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2255500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2636900</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5838400</v>
+      </c>
+      <c r="E44" s="3">
         <v>5870500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5663500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4669200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4964200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4919100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4564000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4680700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4637000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4233100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4130600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4443900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4300400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4454500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4074700</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1368900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2970000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1324200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2294700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1082100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2306000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1040300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1707800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>820100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1454900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>803800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1271200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>647400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1357600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>950900</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26427000</v>
+      </c>
+      <c r="E46" s="3">
         <v>27285400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21188900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19860400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15357500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15683400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13555000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13144600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12355400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11439900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10947600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10837200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11140900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11720500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11547400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10251900</v>
+      </c>
+      <c r="E47" s="3">
         <v>10123400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10131500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9334900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8501900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7963200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8131900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7848200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7173100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6956900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6449300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5838100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>5632800</v>
       </c>
       <c r="P47" s="3">
         <v>5632800</v>
       </c>
       <c r="Q47" s="3">
+        <v>5632800</v>
+      </c>
+      <c r="R47" s="3">
         <v>5195500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24938700</v>
+      </c>
+      <c r="E48" s="3">
         <v>23388500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23587400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21275200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21418400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18463800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18646300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18004500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17307600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16672100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16960900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14949200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15080000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14573700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14145600</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12871800</v>
+      </c>
+      <c r="E49" s="3">
         <v>12789900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12702200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11674600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11088600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9466100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9491000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9618400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9350300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9476800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9672100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9567500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9603900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9972100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10302700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2685,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3875100</v>
+      </c>
+      <c r="E52" s="3">
         <v>4858700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4301700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4656800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3956200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4237400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3644400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4593000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3818900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4084900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3645900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3567200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2953100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3445000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2602400</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>79695300</v>
+      </c>
+      <c r="E54" s="3">
         <v>79728600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73202200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67845800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61384100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56728000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54336900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53896300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>50761200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49291100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48372700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45336800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45027100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45909900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44372200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +2877,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4082900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4171500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3934100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3013800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3008800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3097900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2853500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2391000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2244900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2188300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2296500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2209600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1918700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1916600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1956300</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8709700</v>
+      </c>
+      <c r="E58" s="3">
         <v>9714600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8197600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8051900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8108100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7919700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6592800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5194800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5153500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6024300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5473100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5501600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5145200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5260400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4726700</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5744800</v>
+      </c>
+      <c r="E59" s="3">
         <v>5847000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5003600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5017400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3916900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3978400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3346900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4183500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3511900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3637800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3381100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3160900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2752300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3340500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2978700</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19855800</v>
+      </c>
+      <c r="E60" s="3">
         <v>20289100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18512000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16558100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15829800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15285300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13670800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12117000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11615000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12105400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11871900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11147800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10276700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10735500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10318700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15523600</v>
+      </c>
+      <c r="E61" s="3">
         <v>16533600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15175900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15807900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15127100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13293100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13748700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15346000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14931000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14244700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14591800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13150500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13710400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13496200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13525700</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1865100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2008300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1826800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1834800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1743200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1355500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1248600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1172200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1003300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1274800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1126900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1339900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1257200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1434200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1160800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39492800</v>
+      </c>
+      <c r="E66" s="3">
         <v>40957600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37742000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35964800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34599100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31137800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29987300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29849400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28758300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28734300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28859900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26759900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26539000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26862400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26327900</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23851200</v>
+      </c>
+      <c r="E72" s="3">
         <v>22182500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19004100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16716500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15385900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14406300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12939300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12383800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11065800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10650000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9961700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9185100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8432800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8962700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8137300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30306700</v>
+      </c>
+      <c r="E76" s="3">
         <v>29056900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26527200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23782500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19832200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20110400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19151100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19126500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17399700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16159100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15161100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14151300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13643000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13945300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12895500</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>536300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>1008900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-755700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>533600</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>986300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-690500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>489200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>951900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-610000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>455500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>885800</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4069000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4035100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3334400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3269700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2275600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1726500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1747000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2232800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1689100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1131800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1570600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1328800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1130500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1139700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>975800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1046600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-845800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2259300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-706100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-705200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-703000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-953400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-811200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-807300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-870100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1572200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-909900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1112700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-665500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1520200</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-777300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1878400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1365600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1230200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2972200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1073600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1568400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1105300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-708300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1092800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1379800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1278600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3022100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,55 +4612,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1279000</v>
+      </c>
+      <c r="E96" s="3">
         <v>120900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>460500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>749200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1174500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>107800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>220600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>545800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>946400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>145900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>467400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>170300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>905000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>141600</v>
       </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +4810,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4356400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2183300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1791900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2043000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>69100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>416900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>392000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-943000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-423700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>332800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>45100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-578600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-45400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-230900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1991100</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-56800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>72300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>126600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>69900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>84000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-68800</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1165200</v>
+      </c>
+      <c r="E102" s="3">
         <v>4209900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4040500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-638400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1055200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>578800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>151400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>558800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>361300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>179100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-456100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>211100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-210700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-50100</v>
       </c>
     </row>
